--- a/api/clv1/codelist/Region.xlsx
+++ b/api/clv1/codelist/Region.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="60">
   <si>
     <t>code</t>
   </si>
@@ -79,7 +79,7 @@
     <t>389</t>
   </si>
   <si>
-    <t>North &amp; Central America, regional</t>
+    <t>Caribbean &amp; Central America, regional</t>
   </si>
   <si>
     <t>489</t>
@@ -140,6 +140,60 @@
   </si>
   <si>
     <t>Developing countries, unspecified</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Eastern Africa, regional</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Middle Africa, regional</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Southern Africa, regional</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>Western Africa, regional</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>Caribbean, regional</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>Central America, regional</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>Melanesia, regional</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>Micronesia, regional</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Polynesia, regional</t>
   </si>
 </sst>
 </file>
@@ -471,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -684,6 +738,105 @@
         <v>9</v>
       </c>
     </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
